--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDCB6458-4B68-41FA-833D-4DFC740A0955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E330723C-F4E0-462E-AB23-3EDF6D37AC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B054A0B2-69EF-4FBD-8752-FAB29CE05263}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C5DCE91D-2B2A-4C04-8E81-7CED3373643D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -71,94 +71,94 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w113757307-220_HRV-w89823918-400_HRV</t>
+    <t>e_Knin_HRV</t>
+  </si>
+  <si>
+    <t>e_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>g_Knin_HRV-KastelStari_HRV</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w162022271-220_HRV-w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w163860997-400_HRV-w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w210745193-220_HRV-w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w273326173-220_HRV-w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w273326173-220_HRV-w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-220_HRV-w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-400_HRV-w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-400_HRV-w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89818719-400_HRV-w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89819945-220_HRV-w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89819945-220_HRV-w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89820062-400_HRV-w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w96704507-220_HRV-w170366194-220_HRV</t>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>g_Kutina_HRV-Sisak_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>g_Ogulin_HRV-Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>g_Ogulin_HRV-Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>g_Pula_HRV-Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>g_Rijeka_HRV-Knin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>g_Rijeka_HRV-VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>g_Sesvete_HRV-Sisak_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>g_Sesvete_HRV-Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>g_Sibenik_HRV-Split_HRV</t>
+  </si>
+  <si>
+    <t>g_VelikaGorica_HRV-Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>g_Vinkovci_HRV-Osijek_HRV</t>
+  </si>
+  <si>
+    <t>g_Viskovo_HRV-Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>g_Zagreb_HRV-Osijek_HRV</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -170,46 +170,46 @@
     <t>description</t>
   </si>
   <si>
+    <t>grid link -100.0 km- way/163860997-400;way/43337263-400</t>
+  </si>
+  <si>
+    <t>grid link -45.0 km- way/170366194-220;way/96704507-220</t>
+  </si>
+  <si>
+    <t>grid link -118.0 km- way/273326173-220;way/89819945-220</t>
+  </si>
+  <si>
+    <t>grid link -145.0 km- way/162022271-220;way/273326173-220</t>
+  </si>
+  <si>
+    <t>grid link -47.0 km- way/210745193-220;way/89817617-220</t>
+  </si>
+  <si>
+    <t>grid link -180.0 km- way/163860997-400;way/89817617-400</t>
+  </si>
+  <si>
+    <t>grid link -128.0 km- way/89817617-400;way/89818719-400</t>
+  </si>
+  <si>
+    <t>grid link -44.0 km- way/170366194-220;way/89819945-220</t>
+  </si>
+  <si>
+    <t>grid link -24.0 km- way/89819945-220;way/89820062-400</t>
+  </si>
+  <si>
+    <t>grid link -75.0 km- way/162022271-220;way/43337263-220</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- way/89818719-400;way/89820062-400</t>
+  </si>
+  <si>
     <t>grid link -33.0 km- way/113757307-220;way/89823918-400</t>
   </si>
   <si>
-    <t>grid link -75.0 km- way/162022271-220;way/43337263-220</t>
-  </si>
-  <si>
-    <t>grid link -100.0 km- way/163860997-400;way/43337263-400</t>
-  </si>
-  <si>
-    <t>grid link -47.0 km- way/210745193-220;way/89817617-220</t>
-  </si>
-  <si>
-    <t>grid link -145.0 km- way/162022271-220;way/273326173-220</t>
-  </si>
-  <si>
-    <t>grid link -118.0 km- way/273326173-220;way/89819945-220</t>
-  </si>
-  <si>
     <t>grid link -55.0 km- way/273326173-220;way/89817617-220</t>
   </si>
   <si>
-    <t>grid link -180.0 km- way/163860997-400;way/89817617-400</t>
-  </si>
-  <si>
-    <t>grid link -128.0 km- way/89817617-400;way/89818719-400</t>
-  </si>
-  <si>
-    <t>grid link -61.0 km- way/89818719-400;way/89820062-400</t>
-  </si>
-  <si>
-    <t>grid link -44.0 km- way/170366194-220;way/89819945-220</t>
-  </si>
-  <si>
-    <t>grid link -24.0 km- way/89819945-220;way/89820062-400</t>
-  </si>
-  <si>
     <t>grid link -231.0 km- way/89820062-400;way/89823918-400</t>
-  </si>
-  <si>
-    <t>grid link -45.0 km- way/170366194-220;way/96704507-220</t>
   </si>
   <si>
     <t>~commodity_geo</t>
@@ -679,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101B6526-BF29-49A1-A3D4-6ADB8A5B5FA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2EDAB8-F7A6-423F-8C01-C3159B51704A}">
   <dimension ref="B3:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -764,16 +764,16 @@
         <v>43</v>
       </c>
       <c r="O5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>18.420983798347297</v>
+        <v>16.501279071484671</v>
       </c>
       <c r="R5">
-        <v>45.288705409625472</v>
+        <v>43.60043328704915</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.45">
@@ -805,16 +805,16 @@
         <v>44</v>
       </c>
       <c r="O6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P6" t="s">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>15.903205816155046</v>
+        <v>15.754697507990151</v>
       </c>
       <c r="R6">
-        <v>43.756388757532321</v>
+        <v>44.207396025652962</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
@@ -846,16 +846,16 @@
         <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P7" t="s">
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>15.754697507990151</v>
+        <v>16.913620388699012</v>
       </c>
       <c r="R7">
-        <v>44.207396025652962</v>
+        <v>45.448081289056574</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
@@ -869,34 +869,34 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="P8" t="s">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>16.41378481811703</v>
+        <v>15.105276725972995</v>
       </c>
       <c r="R8">
-        <v>45.452492401724257</v>
+        <v>44.993014847588817</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
@@ -910,10 +910,10 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -928,16 +928,16 @@
         <v>47</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>14.166639022574504</v>
+        <v>18.663329039744493</v>
       </c>
       <c r="R9">
-        <v>45.137590945224346</v>
+        <v>45.473186839980002</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
@@ -951,10 +951,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -969,16 +969,16 @@
         <v>48</v>
       </c>
       <c r="O10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P10" t="s">
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>15.105276725972995</v>
+        <v>14.166639022574504</v>
       </c>
       <c r="R10">
-        <v>44.993014847588817</v>
+        <v>45.137590945224346</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -992,34 +992,34 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
         <v>49</v>
       </c>
       <c r="O11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>16.500996377679218</v>
+        <v>14.564190054501609</v>
       </c>
       <c r="R11">
-        <v>43.600259258254958</v>
+        <v>45.31636366839107</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -1033,10 +1033,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
         <v>29</v>
@@ -1057,10 +1057,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>16.501279071484671</v>
+        <v>16.111889141850742</v>
       </c>
       <c r="R12">
-        <v>43.60043328704915</v>
+        <v>45.667427381860662</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
@@ -1092,16 +1092,16 @@
         <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>14.563904567364178</v>
+        <v>15.903205816155046</v>
       </c>
       <c r="R13">
-        <v>45.316184595349739</v>
+        <v>43.756388757532321</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.45">
@@ -1115,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -1133,16 +1133,16 @@
         <v>52</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>14.564190054501609</v>
+        <v>16.41378481811703</v>
       </c>
       <c r="R14">
-        <v>45.31636366839107</v>
+        <v>45.452492401724257</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
@@ -1156,34 +1156,34 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
         <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>35</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L15" t="s">
         <v>53</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>15.869401606746242</v>
+        <v>16.500996377679218</v>
       </c>
       <c r="R15">
-        <v>45.681428265735541</v>
+        <v>43.600259258254958</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -1197,34 +1197,34 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L16" t="s">
         <v>54</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>16.111889141850742</v>
+        <v>15.869401606746242</v>
       </c>
       <c r="R16">
-        <v>45.667427381860662</v>
+        <v>45.681428265735541</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -1238,34 +1238,34 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
       </c>
       <c r="O17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>16.162877551551272</v>
+        <v>18.420983798347297</v>
       </c>
       <c r="R17">
-        <v>45.876171942571233</v>
+        <v>45.288705409625472</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -1279,10 +1279,10 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
         <v>39</v>
@@ -1297,30 +1297,30 @@
         <v>56</v>
       </c>
       <c r="O18" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>18.663329039744493</v>
+        <v>14.563904567364178</v>
       </c>
       <c r="R18">
-        <v>45.473186839980002</v>
+        <v>45.316184595349739</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O19" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>16.913620388699012</v>
+        <v>16.162877551551272</v>
       </c>
       <c r="R19">
-        <v>45.448081289056574</v>
+        <v>45.876171942571233</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E330723C-F4E0-462E-AB23-3EDF6D37AC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB6D4AD8-F1B2-495F-8FCA-622E5C073CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C5DCE91D-2B2A-4C04-8E81-7CED3373643D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC99F34D-A742-4179-954F-F86EF0631CC2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2EDAB8-F7A6-423F-8C01-C3159B51704A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312FAEAC-F186-4EE0-95BD-05354E68728D}">
   <dimension ref="B3:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB6D4AD8-F1B2-495F-8FCA-622E5C073CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA6596D0-1095-4331-BFFC-BCD9348FEB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AC99F34D-A742-4179-954F-F86EF0631CC2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{50083ED4-9ED9-4B9E-A4B0-44DAC96F6025}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312FAEAC-F186-4EE0-95BD-05354E68728D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594CC602-D97E-4D85-9838-869B172F2864}">
   <dimension ref="B3:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA6596D0-1095-4331-BFFC-BCD9348FEB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D32262-69A1-4280-8148-883D3FBFFDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{50083ED4-9ED9-4B9E-A4B0-44DAC96F6025}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{86E422B2-54AB-4706-B546-EFDDA7EEBC5F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594CC602-D97E-4D85-9838-869B172F2864}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D80C35A-E92C-4A51-8F4A-3B6971A50CD0}">
   <dimension ref="B3:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2D32262-69A1-4280-8148-883D3FBFFDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F50808A2-B62A-4DAC-A1AD-98B73D4C07C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{86E422B2-54AB-4706-B546-EFDDA7EEBC5F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{66E03B78-05C4-4E9C-A797-C0CFC3CCF5B0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D80C35A-E92C-4A51-8F4A-3B6971A50CD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46422F92-1353-4EDF-9F96-EE6F6FA8991A}">
   <dimension ref="B3:R47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F50808A2-B62A-4DAC-A1AD-98B73D4C07C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2E650D-2D69-476D-8B08-CE3B20972D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{66E03B78-05C4-4E9C-A797-C0CFC3CCF5B0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{E9C86C11-1D18-49D1-BB8C-FC9658FB0F8F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
+    <sheet name="co2_links" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="184">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -272,6 +273,39 @@
     <t>elc_spv_HRV_015</t>
   </si>
   <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
+  </si>
+  <si>
     <t>elc_won_HRV_001</t>
   </si>
   <si>
@@ -309,6 +343,255 @@
   </si>
   <si>
     <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>co2_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Vinkovci_HRV-ogci10897</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>co2_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>co2_Knin_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Knin_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>co2_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sisak_HRV-ogci10893</t>
+  </si>
+  <si>
+    <t>co2_Pula_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Pula_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>co2_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Ogulin_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>co2_Split_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Split_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>co2_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_KastelStari_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>co2_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Viskovo_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>co2_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Rijeka_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>co2_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_VelikaGorica_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>co2_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sesvete_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>co2_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Zagreb_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>co2_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Osijek_HRV-ogci10897</t>
+  </si>
+  <si>
+    <t>co2_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10895</t>
+  </si>
+  <si>
+    <t>co2s_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sisak_HRV-ogci10894</t>
+  </si>
+  <si>
+    <t>co2s_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10896</t>
+  </si>
+  <si>
+    <t>co2s_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10898</t>
+  </si>
+  <si>
+    <t>co2s_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Zagreb_HRV-ogci10900</t>
+  </si>
+  <si>
+    <t>co2s_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10901</t>
+  </si>
+  <si>
+    <t>co2s_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Osijek_HRV-ogci10902</t>
+  </si>
+  <si>
+    <t>co2s_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Pula_HRV-ogci10903</t>
+  </si>
+  <si>
+    <t>co2s_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10906</t>
+  </si>
+  <si>
+    <t>co2s_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci11249</t>
+  </si>
+  <si>
+    <t>co2s_ogci11250_HRV</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci11250</t>
+  </si>
+  <si>
+    <t>co2 pipeline -38 km- way/113757307-220 to ogci_10897.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -60 km- way/162022271-220 to ogci_10907.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -97 km- way/163860997-400 to ogci_10907.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -27 km- way/170366194-220 to ogci_10893.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -114 km- way/210745193-220 to ogci_10904.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -153 km- way/273326173-220 to ogci_10899.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -110 km- way/43337263-220 to ogci_10907.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -110 km- way/43337263-400 to ogci_10907.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -155 km- way/89817617-220 to ogci_10904.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -155 km- way/89817617-400 to ogci_10904.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -50 km- way/89818719-400 to ogci_10899.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -28 km- way/89819945-220 to ogci_10899.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -34 km- way/89820062-400 to ogci_10899.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -5 km- way/89823918-400 to ogci_10897.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -50 km- way/96704507-220 to ogci_10895.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -27 km- way/170366194-220 to ogci_10894.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -87 km- way/96704507-220 to ogci_10896.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -74 km- way/162022271-220 to ogci_10898.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -86 km- way/89820062-400 to ogci_10900.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -90 km- way/96704507-220 to ogci_10901.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -61 km- way/89823918-400 to ogci_10902.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -125 km- way/210745193-220 to ogci_10903.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -80 km- way/162022271-220 to ogci_10906.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -81 km- way/162022271-220 to ogci_11249.0</t>
+  </si>
+  <si>
+    <t>co2 pipeline -61 km- way/162022271-220 to ogci_11250.0</t>
   </si>
 </sst>
 </file>
@@ -679,8 +962,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46422F92-1353-4EDF-9F96-EE6F6FA8991A}">
-  <dimension ref="B3:R47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5136CD-B465-4A6B-A4CE-3FABA3A12AFB}">
+  <dimension ref="B3:R58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1541,10 +1824,10 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>17.600065674778687</v>
+        <v>13.803928694655268</v>
       </c>
       <c r="R35">
-        <v>42.947075227327844</v>
+        <v>44.454932217252427</v>
       </c>
     </row>
     <row r="36" spans="15:18" x14ac:dyDescent="0.45">
@@ -1555,10 +1838,10 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>16.579162967152065</v>
+        <v>16.828384390409024</v>
       </c>
       <c r="R36">
-        <v>43.618932251323209</v>
+        <v>42.466360025001833</v>
       </c>
     </row>
     <row r="37" spans="15:18" x14ac:dyDescent="0.45">
@@ -1569,10 +1852,10 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>13.906762304385827</v>
+        <v>18.270796243376044</v>
       </c>
       <c r="R37">
-        <v>45.07863711613124</v>
+        <v>42.125213525162977</v>
       </c>
     </row>
     <row r="38" spans="15:18" x14ac:dyDescent="0.45">
@@ -1583,10 +1866,10 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>14.483886991838087</v>
+        <v>17.506483224613337</v>
       </c>
       <c r="R38">
-        <v>45.331946195599471</v>
+        <v>42.538207099784479</v>
       </c>
     </row>
     <row r="39" spans="15:18" x14ac:dyDescent="0.45">
@@ -1597,10 +1880,10 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>15.809377084060609</v>
+        <v>14.784357229458395</v>
       </c>
       <c r="R39">
-        <v>44.012498899877137</v>
+        <v>43.627676350104089</v>
       </c>
     </row>
     <row r="40" spans="15:18" x14ac:dyDescent="0.45">
@@ -1611,10 +1894,10 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>15.164471200835765</v>
+        <v>15.29247015684356</v>
       </c>
       <c r="R40">
-        <v>44.523125556136428</v>
+        <v>43.591165258465011</v>
       </c>
     </row>
     <row r="41" spans="15:18" x14ac:dyDescent="0.45">
@@ -1625,10 +1908,10 @@
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>15.782157995565388</v>
+        <v>15.968965318614128</v>
       </c>
       <c r="R41">
-        <v>44.348016883150542</v>
+        <v>43.37637801093836</v>
       </c>
     </row>
     <row r="42" spans="15:18" x14ac:dyDescent="0.45">
@@ -1639,10 +1922,10 @@
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>18.335316155297647</v>
+        <v>16.007105690349647</v>
       </c>
       <c r="R42">
-        <v>45.357187206013201</v>
+        <v>42.971078542317287</v>
       </c>
     </row>
     <row r="43" spans="15:18" x14ac:dyDescent="0.45">
@@ -1653,10 +1936,10 @@
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>18.766510818285862</v>
+        <v>16.584950810525882</v>
       </c>
       <c r="R43">
-        <v>45.493689175149086</v>
+        <v>42.966936368464943</v>
       </c>
     </row>
     <row r="44" spans="15:18" x14ac:dyDescent="0.45">
@@ -1667,10 +1950,10 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>16.644419020683017</v>
+        <v>15.32111484630331</v>
       </c>
       <c r="R44">
-        <v>45.640389174848501</v>
+        <v>43.003374766865043</v>
       </c>
     </row>
     <row r="45" spans="15:18" x14ac:dyDescent="0.45">
@@ -1681,10 +1964,10 @@
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>16.058351137930462</v>
+        <v>15.939538105161402</v>
       </c>
       <c r="R45">
-        <v>46.005205111639626</v>
+        <v>42.586922315856633</v>
       </c>
     </row>
     <row r="46" spans="15:18" x14ac:dyDescent="0.45">
@@ -1695,10 +1978,10 @@
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>16.448711926621812</v>
+        <v>17.600065674778687</v>
       </c>
       <c r="R46">
-        <v>46.374206998637192</v>
+        <v>42.947075227327844</v>
       </c>
     </row>
     <row r="47" spans="15:18" x14ac:dyDescent="0.45">
@@ -1709,10 +1992,936 @@
         <v>8</v>
       </c>
       <c r="Q47">
+        <v>16.579162967152065</v>
+      </c>
+      <c r="R47">
+        <v>43.618932251323209</v>
+      </c>
+    </row>
+    <row r="48" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>13.906762304385827</v>
+      </c>
+      <c r="R48">
+        <v>45.07863711613124</v>
+      </c>
+    </row>
+    <row r="49" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O49" t="s">
+        <v>91</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>14.483886991838087</v>
+      </c>
+      <c r="R49">
+        <v>45.331946195599471</v>
+      </c>
+    </row>
+    <row r="50" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>92</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>15.809377084060609</v>
+      </c>
+      <c r="R50">
+        <v>44.012498899877137</v>
+      </c>
+    </row>
+    <row r="51" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>93</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>15.164471200835765</v>
+      </c>
+      <c r="R51">
+        <v>44.523125556136428</v>
+      </c>
+    </row>
+    <row r="52" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>94</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>15.782157995565388</v>
+      </c>
+      <c r="R52">
+        <v>44.348016883150542</v>
+      </c>
+    </row>
+    <row r="53" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>95</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>18.335316155297647</v>
+      </c>
+      <c r="R53">
+        <v>45.357187206013201</v>
+      </c>
+    </row>
+    <row r="54" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>96</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>18.766510818285862</v>
+      </c>
+      <c r="R54">
+        <v>45.493689175149086</v>
+      </c>
+    </row>
+    <row r="55" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O55" t="s">
+        <v>97</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>16.644419020683017</v>
+      </c>
+      <c r="R55">
+        <v>45.640389174848501</v>
+      </c>
+    </row>
+    <row r="56" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O56" t="s">
+        <v>98</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>16.058351137930462</v>
+      </c>
+      <c r="R56">
+        <v>46.005205111639626</v>
+      </c>
+    </row>
+    <row r="57" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>99</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>16.448711926621812</v>
+      </c>
+      <c r="R57">
+        <v>46.374206998637192</v>
+      </c>
+    </row>
+    <row r="58" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>100</v>
+      </c>
+      <c r="P58" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58">
         <v>16.916722421469085</v>
       </c>
-      <c r="R47">
+      <c r="R58">
         <v>45.926508069000413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B39250-7737-4E11-8470-265EC26B4C69}">
+  <dimension ref="B3:L29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" t="s">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" t="s">
+        <v>116</v>
+      </c>
+      <c r="L9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" t="s">
+        <v>119</v>
+      </c>
+      <c r="L10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" t="s">
+        <v>105</v>
+      </c>
+      <c r="K14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" t="s">
+        <v>133</v>
+      </c>
+      <c r="L17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" t="s">
+        <v>144</v>
+      </c>
+      <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="K22" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" t="s">
+        <v>146</v>
+      </c>
+      <c r="L23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+      <c r="K25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G26" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" t="s">
+        <v>105</v>
+      </c>
+      <c r="K26" t="s">
+        <v>152</v>
+      </c>
+      <c r="L26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" t="s">
+        <v>105</v>
+      </c>
+      <c r="K27" t="s">
+        <v>154</v>
+      </c>
+      <c r="L27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" t="s">
+        <v>105</v>
+      </c>
+      <c r="K28" t="s">
+        <v>156</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" t="s">
+        <v>105</v>
+      </c>
+      <c r="K29" t="s">
+        <v>158</v>
+      </c>
+      <c r="L29" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2E650D-2D69-476D-8B08-CE3B20972D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{361B35B5-27DF-4DED-ACDB-1D98EFCA60A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{E9C86C11-1D18-49D1-BB8C-FC9658FB0F8F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{EA857A41-F58E-41EE-A324-E329E77A0F90}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -962,7 +962,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5136CD-B465-4A6B-A4CE-3FABA3A12AFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F50608-5252-4DE7-8C36-930B0A4222BB}">
   <dimension ref="B3:R58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2158,7 +2158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B39250-7737-4E11-8470-265EC26B4C69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC0A552-C2A5-491D-944D-F9502F783A26}">
   <dimension ref="B3:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
